--- a/tests/CREATE_B_measurement/input_template.xlsx
+++ b/tests/CREATE_B_measurement/input_template.xlsx
@@ -1018,7 +1018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I5" s="3">
         <v>0</v>

--- a/tests/CREATE_B_measurement/input_template.xlsx
+++ b/tests/CREATE_B_measurement/input_template.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="3"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="element_types"/>
